--- a/consolidacion/data/pruebas/personas_gestion_riesgo_20260815_0900.xlsx
+++ b/consolidacion/data/pruebas/personas_gestion_riesgo_20260815_0900.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
